--- a/Assets/Resources/MasterData/TextData.xlsx
+++ b/Assets/Resources/MasterData/TextData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\Droad\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9993C2EF-48B3-47D3-9292-FCC5D5B2C121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD9E8F2-A224-4641-8513-620647D23E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1815" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextData" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/MasterData/TextData.xlsx
+++ b/Assets/Resources/MasterData/TextData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\Droad\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD9E8F2-A224-4641-8513-620647D23E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB46421-8029-41F0-B271-95B50D4EC76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1815" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="127">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -221,25 +221,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スター1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スター2</t>
-  </si>
-  <si>
-    <t>スター3</t>
-  </si>
-  <si>
-    <t>スター4</t>
-  </si>
-  <si>
-    <t>スター5</t>
-  </si>
-  <si>
-    <t>スター6</t>
-  </si>
-  <si>
     <t>デッキからカードを{0}枚捨てた</t>
     <rPh sb="12" eb="13">
       <t>マイ</t>
@@ -1295,6 +1276,10 @@
     <rPh sb="10" eb="11">
       <t>ウシナ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スター</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1646,7 +1631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B122"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -1674,7 +1659,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1698,7 +1683,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1730,7 +1715,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1738,7 +1723,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1746,7 +1731,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1754,7 +1739,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1762,7 +1747,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1770,7 +1755,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1778,7 +1763,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1786,7 +1771,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1794,7 +1779,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1802,7 +1787,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1810,7 +1795,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1818,7 +1803,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1826,7 +1811,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1954,7 +1939,7 @@
         <v>115</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1962,7 +1947,7 @@
         <v>116</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1970,7 +1955,7 @@
         <v>117</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1978,7 +1963,7 @@
         <v>118</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1986,7 +1971,7 @@
         <v>119</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1994,7 +1979,7 @@
         <v>120</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2002,7 +1987,7 @@
         <v>121</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2010,7 +1995,7 @@
         <v>122</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2018,7 +2003,7 @@
         <v>123</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2026,7 +2011,7 @@
         <v>124</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2034,7 +2019,7 @@
         <v>125</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2042,7 +2027,7 @@
         <v>126</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2050,7 +2035,7 @@
         <v>127</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2058,7 +2043,7 @@
         <v>128</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2066,7 +2051,7 @@
         <v>129</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2074,7 +2059,7 @@
         <v>130</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2082,7 +2067,7 @@
         <v>131</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2090,7 +2075,7 @@
         <v>132</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2098,7 +2083,7 @@
         <v>133</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2106,7 +2091,7 @@
         <v>134</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2114,7 +2099,7 @@
         <v>135</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2122,7 +2107,7 @@
         <v>136</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2130,7 +2115,7 @@
         <v>137</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2138,7 +2123,7 @@
         <v>138</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2146,7 +2131,7 @@
         <v>139</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2154,7 +2139,7 @@
         <v>140</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2178,7 +2163,7 @@
         <v>202</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2186,7 +2171,7 @@
         <v>203</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2194,7 +2179,7 @@
         <v>300</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2202,7 +2187,7 @@
         <v>301</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2210,7 +2195,7 @@
         <v>302</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2218,7 +2203,7 @@
         <v>303</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2226,7 +2211,7 @@
         <v>304</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2234,7 +2219,7 @@
         <v>305</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2242,7 +2227,7 @@
         <v>306</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2250,7 +2235,7 @@
         <v>307</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2258,7 +2243,7 @@
         <v>308</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2266,7 +2251,7 @@
         <v>309</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2274,7 +2259,7 @@
         <v>310</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2282,7 +2267,7 @@
         <v>311</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2290,7 +2275,7 @@
         <v>312</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2298,7 +2283,7 @@
         <v>313</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2306,7 +2291,7 @@
         <v>314</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2314,7 +2299,7 @@
         <v>315</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2322,7 +2307,7 @@
         <v>316</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2330,7 +2315,7 @@
         <v>317</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2338,7 +2323,7 @@
         <v>318</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2346,7 +2331,7 @@
         <v>319</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2354,7 +2339,7 @@
         <v>320</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2362,7 +2347,7 @@
         <v>321</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2370,7 +2355,7 @@
         <v>322</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2378,7 +2363,7 @@
         <v>323</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2386,84 +2371,84 @@
         <v>324</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>325</v>
+        <v>400</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>326</v>
+        <v>401</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>327</v>
+        <v>402</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>328</v>
+        <v>403</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>329</v>
+        <v>404</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>97</v>
@@ -2471,111 +2456,111 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>109</v>
@@ -2583,50 +2568,10 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" s="2">
-        <v>420</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="2">
-        <v>421</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="2">
-        <v>422</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="2">
-        <v>423</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="2">
-        <v>424</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2643,42 +2588,42 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/MasterData/TextData.xlsx
+++ b/Assets/Resources/MasterData/TextData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\Droad\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB46421-8029-41F0-B271-95B50D4EC76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B151A0-A4A3-41E1-A1AD-E1149DDA11B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="128">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -1280,6 +1280,13 @@
   </si>
   <si>
     <t>スター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果なし</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1631,7 +1638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -1816,761 +1823,769 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>9</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>123</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>113</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>300</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>74</v>
+        <v>203</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>306</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>71</v>
+        <v>305</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>400</v>
+        <v>324</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
+        <v>423</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
         <v>424</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B118" s="2" t="s">
         <v>110</v>
       </c>
     </row>
